--- a/week-01/GTrends_milkshake_hamburger_2024.csv/Ex4C_GTrends_marketing.xlsx
+++ b/week-01/GTrends_milkshake_hamburger_2024.csv/Ex4C_GTrends_marketing.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/sramirez_my_yearupunited_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84620965-31EA-4F2F-BD41-5DC685683840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9463FB92-4ECA-413E-B06A-D06D10D9EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="2016" windowWidth="17040" windowHeight="8916" xr2:uid="{FFC9F9BE-BA05-4A56-BC1B-0ECC51FCB96D}"/>
+    <workbookView xWindow="7944" yWindow="0" windowWidth="15192" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{FFC9F9BE-BA05-4A56-BC1B-0ECC51FCB96D}"/>
   </bookViews>
   <sheets>
     <sheet name="By search term" sheetId="1" r:id="rId1"/>
     <sheet name="By state" sheetId="3" r:id="rId2"/>
+    <sheet name="Sales region lookup" sheetId="4" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By search term'!$A$1:$H$52</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="428" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="70">
   <si>
     <t>RegionID</t>
   </si>
@@ -48,13 +49,13 @@
     <t>Region</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamburger: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milkshake: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakup: </t>
+    <t>Hamburger:</t>
+  </si>
+  <si>
+    <t>Milkshake:</t>
+  </si>
+  <si>
+    <t>Broken heart:</t>
   </si>
   <si>
     <t># of regions</t>
@@ -63,7 +64,7 @@
     <t>Date range</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1/2/24 - 28/2/25</t>
+    <t>2/1/24 - 2/28/25</t>
   </si>
   <si>
     <t>Alabama</t>
@@ -81,28 +82,16 @@
     <t>California</t>
   </si>
   <si>
-    <t>Carolina del Norte</t>
-  </si>
-  <si>
-    <t>Carolina del Sur</t>
-  </si>
-  <si>
     <t>Colorado</t>
   </si>
   <si>
     <t>Connecticut</t>
   </si>
   <si>
-    <t>Dakota del Norte</t>
-  </si>
-  <si>
-    <t>Dakota del Sur</t>
-  </si>
-  <si>
     <t>Delaware</t>
   </si>
   <si>
-    <t>Distrito de Columbia</t>
+    <t>District of Columbia</t>
   </si>
   <si>
     <t>Florida</t>
@@ -132,10 +121,7 @@
     <t>Kentucky</t>
   </si>
   <si>
-    <t>Luisiana</t>
-  </si>
-  <si>
-    <t>MÃ­chigan</t>
+    <t>Louisiana</t>
   </si>
   <si>
     <t>Maine</t>
@@ -147,13 +133,16 @@
     <t>Massachusetts</t>
   </si>
   <si>
+    <t>Michigan</t>
+  </si>
+  <si>
     <t>Minnesota</t>
   </si>
   <si>
-    <t>Misisipi</t>
-  </si>
-  <si>
-    <t>Misuri</t>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Missouri</t>
   </si>
   <si>
     <t>Montana</t>
@@ -165,16 +154,22 @@
     <t>Nevada</t>
   </si>
   <si>
-    <t>Nueva Jersey</t>
-  </si>
-  <si>
-    <t>Nueva York</t>
-  </si>
-  <si>
-    <t>Nuevo Hampshire</t>
-  </si>
-  <si>
-    <t>Nuevo MÃ©xico</t>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
   <si>
     <t>Ohio</t>
@@ -186,12 +181,18 @@
     <t>Oregon</t>
   </si>
   <si>
-    <t>Pensilvania</t>
+    <t>Pennsylvania</t>
   </si>
   <si>
     <t>Rhode Island</t>
   </si>
   <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
     <t>Tennessee</t>
   </si>
   <si>
@@ -207,23 +208,56 @@
     <t>Virginia</t>
   </si>
   <si>
-    <t>Virginia Occidental</t>
-  </si>
-  <si>
     <t>Washington</t>
   </si>
   <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
     <t>Wisconsin</t>
   </si>
   <si>
     <t>Wyoming</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Sales Region</t>
+  </si>
+  <si>
+    <t>Hamburger</t>
+  </si>
+  <si>
+    <t>Milkshake</t>
+  </si>
+  <si>
+    <t>Northwest</t>
+  </si>
+  <si>
+    <t>North Central</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of Hamburger</t>
+  </si>
+  <si>
+    <t>Sum of Milkshake</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,15 +396,21 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="35">
@@ -561,7 +601,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,7 +722,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -725,36 +765,28 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -794,6 +826,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="42" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -809,6 +842,1385 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Ex4C_GTrends_marketing.xlsx]Sales region lookup!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sales region lookup'!$B$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Hamburger</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sales region lookup'!$A$16:$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Idaho</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Michigan</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Minnesota</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Montana</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nebraska</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>North Dakota</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Oregon</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>South Dakota</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Washington</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Wisconsin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sales region lookup'!$B$16:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-887F-41B8-AB1D-5323C6ABE600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sales region lookup'!$C$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Milkshake</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sales region lookup'!$A$16:$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Idaho</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Michigan</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Minnesota</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Montana</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nebraska</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>North Dakota</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Oregon</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>South Dakota</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Washington</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Wisconsin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sales region lookup'!$C$16:$C$26</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-887F-41B8-AB1D-5323C6ABE600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1379059552"/>
+        <c:axId val="1379058592"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1379059552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1379058592"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1379058592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1379059552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>624840</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BF18E93-2E3C-A3D7-8A23-E24B3A9060FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="sthef" refreshedDate="46124.939805208334" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{13A064D8-843F-4C7F-9B3F-9CF7F413C1A4}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D11" sheet="Sales region lookup"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="State" numFmtId="0">
+      <sharedItems count="10">
+        <s v="Washington"/>
+        <s v="Oregon"/>
+        <s v="Idaho"/>
+        <s v="Montana"/>
+        <s v="North Dakota"/>
+        <s v="South Dakota"/>
+        <s v="Nebraska"/>
+        <s v="Minnesota"/>
+        <s v="Wisconsin"/>
+        <s v="Michigan"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sales Region" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Northwest"/>
+        <s v="North Central"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Hamburger" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.74" maxValue="0.83"/>
+    </cacheField>
+    <cacheField name="Milkshake" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.15" maxValue="0.24"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0.77"/>
+    <n v="0.21"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0.76"/>
+    <n v="0.22"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0.76"/>
+    <n v="0.22"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0.83"/>
+    <n v="0.15"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="0.78"/>
+    <n v="0.2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="0.83"/>
+    <n v="0.15"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="0.78"/>
+    <n v="0.2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="0.77"/>
+    <n v="0.21"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="0.76"/>
+    <n v="0.22"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="0.74"/>
+    <n v="0.24"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{161CA530-2DE0-4CE2-9F72-7C38563E5D32}" name="PivotTable1" cacheId="428" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="2"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="9" showAll="0"/>
+    <pivotField dataField="1" numFmtId="9" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sum of Hamburger" fld="2" baseField="0" baseItem="0" numFmtId="9"/>
+    <dataField name="Sum of Milkshake" fld="3" baseField="0" baseItem="0" numFmtId="9"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1128,919 +2540,1032 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE7AD66-05C5-442C-9F9B-0B7DAA54B55C}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultColWidth="19.28515625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" customWidth="1"/>
+    <col min="3" max="5" width="19.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.9">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7">
+      <c r="H1" s="10">
         <f>COUNTA(B2:B52)</f>
         <v>51</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.12</v>
+      <c r="C2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="5">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2">
-        <v>0.72</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.13</v>
+      <c r="C3" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="5">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C4" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.13</v>
+      <c r="C5" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="5">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.16</v>
+      <c r="C6" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="5">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.12</v>
+      <c r="C7" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.12</v>
+      <c r="C8" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.15</v>
+      <c r="C9" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="5">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C10" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2">
-        <v>0.69</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.12</v>
+      <c r="C11" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.11</v>
+      <c r="C12" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.13</v>
+      <c r="C13" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.17</v>
+      <c r="C14" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C15" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C16" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.13</v>
+      <c r="C17" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.13</v>
+      <c r="C18" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C19" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C20" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.13</v>
+      <c r="C21" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C22" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C23" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0.13</v>
+      <c r="C24" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="C25" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="D25" s="7">
         <v>0.21</v>
       </c>
-      <c r="E25" s="2">
-        <v>0.12</v>
+      <c r="E25" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0.13</v>
+      <c r="C26" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.15</v>
+      <c r="C27" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0.17</v>
+      <c r="C28" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0.13</v>
+      <c r="C29" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5">
+      <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.12</v>
+      <c r="C30" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0.13</v>
+      <c r="C31" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0.12</v>
+      <c r="C32" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="D32" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5">
+      <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="E33" s="2">
-        <v>0.12</v>
+      <c r="C33" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0.13</v>
+      <c r="C34" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5">
+      <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E35" s="2">
-        <v>0.16</v>
+      <c r="C35" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E36" s="2">
-        <v>0.16</v>
+      <c r="C36" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E37" s="2">
-        <v>0.13</v>
+      <c r="C37" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="5">
+      <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E38" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C38" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="5">
+      <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="D39" s="2">
+      <c r="C39" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D39" s="7">
         <v>0.22</v>
       </c>
-      <c r="E39" s="2">
-        <v>0.13</v>
+      <c r="E39" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="5">
+      <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="2">
-        <v>0.71</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="E40" s="2">
-        <v>0.11</v>
+      <c r="C40" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="5">
+      <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="2">
-        <v>0.69</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="E41" s="2">
-        <v>0.13</v>
+      <c r="C41" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="5">
+      <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E42" s="2">
-        <v>0.15</v>
+      <c r="C42" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="5">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C43" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="5">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0.13</v>
+      <c r="C44" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="5">
+      <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0.13</v>
+      <c r="C45" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="5">
+      <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E46" s="2">
-        <v>0.13</v>
+      <c r="C46" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="5">
+      <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C47" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D47" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="5">
+      <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E48" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C48" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="5">
+      <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E49" s="2">
-        <v>0.12</v>
+      <c r="C49" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="5">
+      <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="D50" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C50" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="5">
+      <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E51" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C51" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="5">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="2">
-        <v>0.69</v>
-      </c>
-      <c r="D52" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="E52" s="2">
-        <v>0.14000000000000001</v>
+      <c r="C52" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="5"/>
-    </row>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+    </row>
+    <row r="65" customFormat="1"/>
+    <row r="66" customFormat="1"/>
+    <row r="67" customFormat="1"/>
+    <row r="68" customFormat="1"/>
+    <row r="69" customFormat="1"/>
+    <row r="70" customFormat="1"/>
+    <row r="71" customFormat="1"/>
+    <row r="72" customFormat="1"/>
+    <row r="73" customFormat="1"/>
+    <row r="74" customFormat="1"/>
+    <row r="75" customFormat="1"/>
+    <row r="76" customFormat="1"/>
+    <row r="77" customFormat="1"/>
+    <row r="78" customFormat="1"/>
+    <row r="79" customFormat="1"/>
+    <row r="80" customFormat="1"/>
+    <row r="81" customFormat="1"/>
+    <row r="82" customFormat="1"/>
+    <row r="83" customFormat="1"/>
+    <row r="84" customFormat="1"/>
+    <row r="85" customFormat="1"/>
+    <row r="86" customFormat="1"/>
+    <row r="87" customFormat="1"/>
+    <row r="88" customFormat="1"/>
+    <row r="89" customFormat="1"/>
+    <row r="90" customFormat="1"/>
+    <row r="91" customFormat="1"/>
+    <row r="92" customFormat="1"/>
+    <row r="93" customFormat="1"/>
+    <row r="94" customFormat="1"/>
+    <row r="95" customFormat="1"/>
+    <row r="96" customFormat="1"/>
+    <row r="97" customFormat="1"/>
+    <row r="98" customFormat="1"/>
+    <row r="99" customFormat="1"/>
+    <row r="100" customFormat="1"/>
+    <row r="101" customFormat="1"/>
+    <row r="102" customFormat="1"/>
+    <row r="103" customFormat="1"/>
+    <row r="104" customFormat="1"/>
+    <row r="105" customFormat="1"/>
+    <row r="106" customFormat="1"/>
+    <row r="107" customFormat="1"/>
+    <row r="108" customFormat="1"/>
+    <row r="109" customFormat="1"/>
+    <row r="110" customFormat="1"/>
+    <row r="111" customFormat="1"/>
+    <row r="112" customFormat="1"/>
+    <row r="113" customFormat="1"/>
+    <row r="114" customFormat="1"/>
+    <row r="115" customFormat="1"/>
+    <row r="116" customFormat="1"/>
+    <row r="117" customFormat="1"/>
+    <row r="118" customFormat="1"/>
+    <row r="119" customFormat="1"/>
+    <row r="120" customFormat="1"/>
+    <row r="121" customFormat="1"/>
+    <row r="122" customFormat="1"/>
+    <row r="123" customFormat="1"/>
+    <row r="124" customFormat="1"/>
+    <row r="125" customFormat="1"/>
   </sheetData>
-  <autoFilter ref="A1:H52" xr:uid="{6BE7AD66-05C5-442C-9F9B-0B7DAA54B55C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D52">
-    <sortCondition ref="B1:B52"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2049,10 +3574,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1592F67F-7C8E-4CD5-B9E7-C516BBE11DA7}">
   <dimension ref="A1:AZ4"/>
-  <sheetFormatPr defaultColWidth="11.28515625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="16.7109375" defaultRowHeight="14.45"/>
   <sheetData>
     <row r="1" spans="1:52">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
@@ -2209,482 +3734,812 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:52" ht="28.9">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:52">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="7">
         <v>0.72</v>
       </c>
-      <c r="D2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.69</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="C2" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="F2" s="7">
         <v>0.75</v>
       </c>
-      <c r="M2" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="G2" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="H2" s="7">
         <v>0.73</v>
       </c>
-      <c r="R2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="X2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="AF2" s="2">
+      <c r="I2" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="L2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="P2" s="7">
         <v>0.73</v>
       </c>
-      <c r="AG2" s="2">
+      <c r="Q2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="T2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="U2" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="V2" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="W2" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="X2" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="AE2" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="AF2" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="AG2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="AH2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AI2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AJ2" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="AK2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AL2" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="AM2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="AN2" s="7">
         <v>0.7</v>
       </c>
-      <c r="AH2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="AL2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="AM2" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>0.71</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>0.69</v>
-      </c>
-      <c r="AP2" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="AQ2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="AS2" s="2">
-        <v>0.67</v>
-      </c>
-      <c r="AT2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="AU2" s="2">
+      <c r="AO2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AP2" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="AQ2" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="AR2" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="AS2" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="AT2" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="AU2" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="AV2" s="7">
         <v>0.7</v>
       </c>
-      <c r="AV2" s="2">
-        <v>0.63</v>
-      </c>
-      <c r="AW2" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="AX2" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="AZ2" s="2">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52" ht="28.9">
-      <c r="A3" s="4" t="s">
+      <c r="AW2" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="AX2" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="AY2" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="AZ2" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E3" s="7">
         <v>0.24</v>
       </c>
-      <c r="C3" s="2">
+      <c r="F3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="L3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="M3" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="N3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="O3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="S3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="T3" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="U3" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="V3" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="W3" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="X3" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="Y3" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="AB3" s="7">
         <v>0.15</v>
       </c>
-      <c r="D3" s="2">
+      <c r="AC3" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="AD3" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="AE3" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="AF3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="AG3" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="AH3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="AI3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="AJ3" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="AK3" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="AL3" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="AM3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="AN3" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="AP3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="AQ3" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="AR3" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="AS3" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="AT3" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="AU3" s="7">
         <v>0.19</v>
       </c>
-      <c r="E3" s="2">
+      <c r="AV3" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="AW3" s="7">
         <v>0.21</v>
       </c>
-      <c r="F3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="AX3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="AY3" s="7">
         <v>0.22</v>
       </c>
-      <c r="H3" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="S3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="T3" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="U3" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="V3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="W3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="X3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="AE3" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="AF3" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="AG3" s="2">
+      <c r="AZ3" s="7">
         <v>0.18</v>
       </c>
-      <c r="AH3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AI3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="AJ3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="AK3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AL3" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="AM3" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="AN3" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="AO3" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="AP3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="AQ3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="AR3" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="AS3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AT3" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="AU3" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="AV3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="AW3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="AX3" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="AY3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AZ3" s="2">
-        <v>0.17</v>
-      </c>
     </row>
     <row r="4" spans="1:52">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="S4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="T4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="V4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="W4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="X4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="AB4" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="AC4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AD4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="AE4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AF4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="AG4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="AH4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AI4" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="AJ4" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="AK4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AL4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AM4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AN4" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="AO4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AP4" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="AQ4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AR4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AS4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AT4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="AU4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AV4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AW4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="AX4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AZ4" s="2">
-        <v>0.14000000000000001</v>
+      <c r="B4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="T4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="V4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="W4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="X4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AG4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AH4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AI4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AJ4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AK4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AL4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AM4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AN4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AO4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AP4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AQ4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AR4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AS4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AT4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AU4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AV4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AW4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AX4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="AY4" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AZ4" s="7">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF60AA40-CBCC-4D17-BA4E-0559B75A6042}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="15.140625" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="6">
+        <f>VLOOKUP('Sales region lookup'!A2, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.77</v>
+      </c>
+      <c r="D2" s="11">
+        <f>_xlfn.XLOOKUP(A2, 'By search term'!B1:B52, 'By search term'!D1:D52, "not found")</f>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="6">
+        <f>VLOOKUP('Sales region lookup'!A3, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.76</v>
+      </c>
+      <c r="D3" s="11">
+        <f>_xlfn.XLOOKUP(A3, 'By search term'!B2:B53, 'By search term'!D2:D53, "not found")</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="6">
+        <f>VLOOKUP('Sales region lookup'!A4, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.76</v>
+      </c>
+      <c r="D4" s="11">
+        <f>_xlfn.XLOOKUP(A4, 'By search term'!B3:B54, 'By search term'!D3:D54, "not found")</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="6">
+        <f>VLOOKUP('Sales region lookup'!A5, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.83</v>
+      </c>
+      <c r="D5" s="11">
+        <f>_xlfn.XLOOKUP(A5, 'By search term'!B4:B55, 'By search term'!D4:D55, "not found")</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="6">
+        <f>VLOOKUP('Sales region lookup'!A6, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.78</v>
+      </c>
+      <c r="D6" s="11">
+        <f>_xlfn.XLOOKUP(A6, 'By search term'!B5:B56, 'By search term'!D5:D56, "not found")</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="6">
+        <f>VLOOKUP('Sales region lookup'!A7, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.83</v>
+      </c>
+      <c r="D7" s="11">
+        <f>_xlfn.XLOOKUP(A7, 'By search term'!B6:B57, 'By search term'!D6:D57, "not found")</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="6">
+        <f>VLOOKUP('Sales region lookup'!A8, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.78</v>
+      </c>
+      <c r="D8" s="11">
+        <f>_xlfn.XLOOKUP(A8, 'By search term'!B7:B58, 'By search term'!D7:D58, "not found")</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" customHeight="1">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="6">
+        <f>VLOOKUP('Sales region lookup'!A9, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.77</v>
+      </c>
+      <c r="D9" s="11">
+        <f>_xlfn.XLOOKUP(A9, 'By search term'!B8:B59, 'By search term'!D8:D59, "not found")</f>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="6">
+        <f>VLOOKUP('Sales region lookup'!A10, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.76</v>
+      </c>
+      <c r="D10" s="11">
+        <f>_xlfn.XLOOKUP(A10, 'By search term'!B9:B60, 'By search term'!D9:D60, "not found")</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="6">
+        <f>VLOOKUP('Sales region lookup'!A11, 'By search term'!B:C, 2, FALSE)</f>
+        <v>0.74</v>
+      </c>
+      <c r="D11" s="11">
+        <f>_xlfn.XLOOKUP(A11, 'By search term'!B10:B61, 'By search term'!D10:D61, "not found")</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="7">
+        <v>7.7799999999999994</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
